--- a/.claude/skills/orcamentista-marcenaria/projetos/orcamento-camila-lavinia.xlsx
+++ b/.claude/skills/orcamentista-marcenaria/projetos/orcamento-camila-lavinia.xlsx
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B9" s="19" t="n">
-        <v>49270</v>
+        <v>47460</v>
       </c>
       <c r="D9" s="102" t="n"/>
       <c r="F9" s="21" t="n"/>
@@ -2578,7 +2578,7 @@
         <v>3</v>
       </c>
       <c r="C100" s="97" t="n">
-        <v>250</v>
+        <v>60</v>
       </c>
       <c r="D100" s="91">
         <f>SUM(B100*C100)</f>

--- a/.claude/skills/orcamentista-marcenaria/projetos/orcamento-camila-lavinia.xlsx
+++ b/.claude/skills/orcamentista-marcenaria/projetos/orcamento-camila-lavinia.xlsx
@@ -5613,9 +5613,7 @@
           <t>Cava 35° usinada no mdf - mt linear</t>
         </is>
       </c>
-      <c r="B282" s="99" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="B282" s="99" t="n"/>
       <c r="C282" s="100" t="n">
         <v>50</v>
       </c>
